--- a/PMI-DZT2/ПМИ ГЗ/pmi_gzdzt/dtm_modes/ДТм_1.xlsx
+++ b/PMI-DZT2/ПМИ ГЗ/pmi_gzdzt/dtm_modes/ДТм_1.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,18 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,16 +72,37 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,219 +517,219 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_prvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_shvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_levptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_lvalh</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_lvalh</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_lvalh</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>SGF4_lvalh</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>SGF5_lvalh</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>SGF6_lvalh</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>SGF7_lvalh</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>SGF8_lvalh</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>SGF9_lvalh</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>SGF10_lvalh</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>SGF11_lvalh</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>SGF12_lvalh</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>SGF13_lvalh</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_tsa</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_tsa</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_tsa</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>SGF4_tsa</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>SGF5_tsa</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>SGF6_tsa</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>SGF7_tsa</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>SGF8_tsa</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>SGF9_tsa</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>SGF10_tsa</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>SGF11_tsa</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>SGF12_tsa</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>SGF13_tsa</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_LowIsolTripCtrl</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_LowIsolTripCtrl</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_LowIsolTripCtrl</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_PRVLVPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_SHVLVPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_LEVPTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_LowIsolSignCtrl</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_LowIsolTripCtrl</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_LowIsolTripCtrl</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_EnaDis</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_EnaDis</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA1</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA2</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA3</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SA4</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SG1</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SG2</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_SG3</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_GAS_OCControl_SG1</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_TECH_OCControl_SG1</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_ARCnn1_OCControl</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_ARCnn2_OCControl</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_CBFPnn1_OCControl</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_Ctl_CBFPnn2_OCControl</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_GASSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_LowIsolGAS_Ctl</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_GASBlock_Ctl</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_TECHSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_LowIsolTECH_Ctl</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_TECHBlock_Ctl</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_ALMSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_OCSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_OCnnSign_Ctl</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_OpExt_Ctl</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_CtlCir_Ctl</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_TestBlock_Ctl</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_ExtSignGen_Ctl</t>
         </is>
       </c>
     </row>
@@ -852,24 +885,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>T1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>T1_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>T1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>T1_tltcgaslgc</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_LLN0_TopOnBlk</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_TopOnBlk</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_LLN0_TopOnBlk</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_LLN0_TopOnBlk</t>
         </is>
       </c>
     </row>
@@ -957,269 +990,269 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VYVOD</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tz</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>OV_dtm</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>OV_dto</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>OV_rd</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_dtm</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_dto</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_rd</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontOtkl_m</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontSign_m</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontOtkl_o</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontSign_o</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontOtkl_rd</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>srabKI_m</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>srabKI_o</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>srabKI_rd</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Sbros</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ts</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>OV_pk</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ok</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>OV_lev</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_pk</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_ok</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_lev</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontOtkl_pk</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontOtkl_ok</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>srabKontOtkl_lev</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>NaOtkl_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>srabKont_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>srabKI_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>srabKont_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>srabKI_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>NaSign_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>srabKont_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>srabKI_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>OV_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>OV_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>OV_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>oil_t_hi_level</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>oil_ltc_hi_level</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>oil_ltc_lo_level</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>oil_ltc_lo_temp</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>otkaz_so</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>neisp_so</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otk_zdz1</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otk_zdz2</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otk_urov1</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otk_urov2</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>vnesh_otkl_so</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>DI_ControllerDisable</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DI_APTTECHLGC</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>DI_OILPTRC</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>DI_WINPTRC</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>DI_VLVPTRC</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>DI_OILPTRC_Sign</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>DI_WINPTRC_Sign</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>DI_VLVPTRC_Sign</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>OILTempEmerg</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>OILTempHigh</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>WINTempEmerg</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>WINTempHigh</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>VLVop</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>OILIsolOp</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>WINIsolOp</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>VLVIsolOp</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Reset</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>DI_ALMTECHLGC</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>DI_PRVLVPTRC1</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>DI_SHVLVPTRC1</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LEVPTRC1</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>DI_PRVLVPTRC1_Sign</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>DI_SHVLVPTRC1_Sign</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>DI_LEVPTRC1_Sign</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>PRVLVOp</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>SHVLVOp</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>LowOILLevel</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TALMGASLGC</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TALMGASLGC_Sign</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>SignContact</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>GASSignIsolOp</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TTRGASLGC</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TTRGASLGC_Sign</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>TripContact</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>GASTripIsolOp</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TLTCGASLGC</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TLTCGASLGC_Sign</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>JetRelayContact</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>GASLTCIsolOp</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TPRMOFFLVLGC</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>DI_TJNTPTRC</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>DI_JNTRBRE</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>HighOILLevel</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>HighOILLevelLTC</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
+        <is>
+          <t>LowOILLevelLTC</t>
+        </is>
+      </c>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>OILTempLowLTC</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>FailCoolSys</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>ProblemCoolSys</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfARC_NN1</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfARC_NN2</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfCBFP_NN1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>OpExtOfCBFP_NN2</t>
+        </is>
+      </c>
+      <c r="BA1" s="4" t="inlineStr">
+        <is>
+          <t>OpExtOfCoolSys</t>
         </is>
       </c>
     </row>
@@ -1466,329 +1499,329 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>srab_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>zablok_oilptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>srab_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>zablok_winptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>srab_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>zablok_vlvptrc1_apttechlgc</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_prvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_prvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>srab_prvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_prvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_shvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_shvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>srab_shvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_shvlvptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_levptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_levptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>srab_levptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_levptrc1_almtechlgc</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>zablok_ptrc1_talmgaslgc</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>zablok_ptrc1_ttrgaslgc</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>srabsign_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>zablok_ptrc1_tltcgaslgc</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_OpOIL</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_OILPTRC1_BlockOIL</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_OpWIN</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_WINPTRC1_BlockWIN</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_OpVLV</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>APTTECHLGC_1_VLVPTRC1_BlockVLV</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_PRVLVPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_PRVLVPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_PRVLVPTRC1_Op</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_PRVLVPTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_SHVLVPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_SHVLVPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_SHVLVPTRC1_Op</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_SHVLVPTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_LEVPTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_LEVPTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_LEVPTRC1_Op</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>ALMTECHLGC_UIRZ_1_LEVPTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_Op</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="AF1" s="3" t="inlineStr">
+        <is>
+          <t>TALMGASLGC_1_PTRC1_BlockGASProtSign</t>
+        </is>
+      </c>
+      <c r="AG1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AH1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_Op</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="AK1" s="3" t="inlineStr">
+        <is>
+          <t>TTRGASLGC_1_PTRC1_BlockGASProtTrip</t>
+        </is>
+      </c>
+      <c r="AL1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AM1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AN1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_Op</t>
+        </is>
+      </c>
+      <c r="AO1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_OpOnSignal</t>
+        </is>
+      </c>
+      <c r="AP1" s="3" t="inlineStr">
+        <is>
+          <t>TLTCGASLGC_1_PTRC1_BlockGASLTCProt</t>
+        </is>
+      </c>
+      <c r="AQ1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AR1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AS1" s="3" t="inlineStr">
         <is>
           <t>pusk_ptrc1_tprmofflvlgc</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>zapret_rbre1_tprmofflvlgc</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>SS_gz_sign</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>SS_gz_nizk_isol</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>SS_gz_zablok</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>SS_tz_sign</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>SS_tz_nizk_isol</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>SS_tz_zablok</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>SS_ts_sign</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>SS_vnesh_otkl</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>SS_vyh_zepi_razobr</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>SS_bi_vyved</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>SS_ot_sign</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>SS_neispr_ot_gz</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>SS_neispr_ot_tz</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>SS_ot_nn_sign</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>SS_obsh_vnesh_sign</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>pusk_lvalh</t>
+      <c r="AT1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_PTRC1_Op</t>
+        </is>
+      </c>
+      <c r="AU1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncEnabled</t>
+        </is>
+      </c>
+      <c r="AV1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_FuncOperDisabled</t>
+        </is>
+      </c>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>TPRMOFFLVLGC_1_RBRE1_BlkOp</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_GASSign</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_LowIsolGAS</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_GASBlock</t>
+        </is>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TECHSign</t>
+        </is>
+      </c>
+      <c r="BB1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_LowIsolTECH</t>
+        </is>
+      </c>
+      <c r="BC1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TECHBlock</t>
+        </is>
+      </c>
+      <c r="BD1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_ALMSign</t>
+        </is>
+      </c>
+      <c r="BE1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_OpExt</t>
+        </is>
+      </c>
+      <c r="BF1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_CtlCir</t>
+        </is>
+      </c>
+      <c r="BG1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TestBlock</t>
+        </is>
+      </c>
+      <c r="BH1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_OCSign</t>
+        </is>
+      </c>
+      <c r="BI1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_GAS_OCControlSignAssem</t>
+        </is>
+      </c>
+      <c r="BJ1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_TECH_OCControlSignAssem</t>
+        </is>
+      </c>
+      <c r="BK1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_OCnnSign</t>
+        </is>
+      </c>
+      <c r="BL1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_SignAssembly_1_ExtSignGen</t>
+        </is>
+      </c>
+      <c r="BM1" s="3" t="inlineStr">
+        <is>
+          <t>DZT2_LVALH_1_CALH1_Alarm</t>
         </is>
       </c>
     </row>
